--- a/Avancado/3 - FUNÇÕES DE TEXTO E DATA/FUNÇÕES DE DATA E HORA.xlsx
+++ b/Avancado/3 - FUNÇÕES DE TEXTO E DATA/FUNÇÕES DE DATA E HORA.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\ALUNOS_FIC\LINELSON.ALUNOS\3 - FUNÇÕES DE TEXTO E DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wilck.alunos\Desktop\EXCEL-completo\Avancado\3 - FUNÇÕES DE TEXTO E DATA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FFC4349-412A-48E7-9331-FAD4EA9BE8FC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC8542A9-DC98-4849-A5C5-29EB83ACAFD1}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11325" activeTab="1" xr2:uid="{D3F35059-5AC7-44FF-9EA5-8241CDA4E646}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="2" xr2:uid="{D3F35059-5AC7-44FF-9EA5-8241CDA4E646}"/>
   </bookViews>
   <sheets>
     <sheet name="FUNÇÕES DATA 1" sheetId="1" r:id="rId1"/>
@@ -247,7 +247,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -327,6 +327,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -695,11 +698,26 @@
       <c r="B3" s="5">
         <v>23525</v>
       </c>
-      <c r="C3" s="9"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
+      <c r="C3" s="9">
+        <f>YEAR(B3)</f>
+        <v>1964</v>
+      </c>
+      <c r="D3" s="2">
+        <f>MONTH(B3)</f>
+        <v>5</v>
+      </c>
+      <c r="E3" s="2">
+        <f>DAY(B3)</f>
+        <v>28</v>
+      </c>
+      <c r="F3" s="2">
+        <f ca="1">DATEDIF(B3,TODAY(),"Y")</f>
+        <v>61</v>
+      </c>
+      <c r="G3" s="32">
+        <f ca="1">_xlfn.DAYS(TODAY(),B3)</f>
+        <v>22574</v>
+      </c>
     </row>
     <row r="4" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
@@ -708,11 +726,26 @@
       <c r="B4" s="5">
         <v>30647</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
+      <c r="C4" s="9">
+        <f t="shared" ref="C4:C8" si="0">YEAR(B4)</f>
+        <v>1983</v>
+      </c>
+      <c r="D4" s="2">
+        <f t="shared" ref="D4:D8" si="1">MONTH(B4)</f>
+        <v>11</v>
+      </c>
+      <c r="E4" s="2">
+        <f t="shared" ref="E4:E8" si="2">DAY(B4)</f>
+        <v>27</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" ref="F4:F8" ca="1" si="3">DATEDIF(B4,TODAY(),"Y")</f>
+        <v>42</v>
+      </c>
+      <c r="G4" s="32">
+        <f t="shared" ref="G4:G8" ca="1" si="4">_xlfn.DAYS(TODAY(),B4)</f>
+        <v>15452</v>
+      </c>
     </row>
     <row r="5" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -721,11 +754,26 @@
       <c r="B5" s="5">
         <v>25727</v>
       </c>
-      <c r="C5" s="9"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
+      <c r="C5" s="9">
+        <f t="shared" si="0"/>
+        <v>1970</v>
+      </c>
+      <c r="D5" s="2">
+        <f t="shared" si="1"/>
+        <v>6</v>
+      </c>
+      <c r="E5" s="2">
+        <f t="shared" si="2"/>
+        <v>8</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" ca="1" si="3"/>
+        <v>55</v>
+      </c>
+      <c r="G5" s="32">
+        <f t="shared" ca="1" si="4"/>
+        <v>20372</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
@@ -734,11 +782,26 @@
       <c r="B6" s="5">
         <v>41011</v>
       </c>
-      <c r="C6" s="9"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
+      <c r="C6" s="9">
+        <f t="shared" si="0"/>
+        <v>2012</v>
+      </c>
+      <c r="D6" s="2">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E6" s="2">
+        <f t="shared" si="2"/>
+        <v>12</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" ca="1" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="G6" s="32">
+        <f t="shared" ca="1" si="4"/>
+        <v>5088</v>
+      </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
@@ -747,11 +810,26 @@
       <c r="B7" s="5">
         <v>42617</v>
       </c>
-      <c r="C7" s="9"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
+      <c r="C7" s="9">
+        <f t="shared" si="0"/>
+        <v>2016</v>
+      </c>
+      <c r="D7" s="2">
+        <f t="shared" si="1"/>
+        <v>9</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" ca="1" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="G7" s="32">
+        <f t="shared" ca="1" si="4"/>
+        <v>3482</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
@@ -760,11 +838,26 @@
       <c r="B8" s="5">
         <v>27264</v>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
+      <c r="C8" s="9">
+        <f t="shared" si="0"/>
+        <v>1974</v>
+      </c>
+      <c r="D8" s="2">
+        <f t="shared" si="1"/>
+        <v>8</v>
+      </c>
+      <c r="E8" s="2">
+        <f t="shared" si="2"/>
+        <v>23</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" ca="1" si="3"/>
+        <v>51</v>
+      </c>
+      <c r="G8" s="32">
+        <f t="shared" ca="1" si="4"/>
+        <v>18835</v>
+      </c>
     </row>
     <row r="9" spans="1:7" s="3" customFormat="1" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -806,60 +899,98 @@
       <c r="A4" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="5"/>
-      <c r="C4" s="16"/>
+      <c r="B4" s="5">
+        <f ca="1">TODAY()</f>
+        <v>46099</v>
+      </c>
+      <c r="C4" s="16">
+        <f ca="1">B5</f>
+        <v>46099.909397222225</v>
+      </c>
       <c r="D4" s="11"/>
     </row>
     <row r="5" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="14"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="25"/>
+      <c r="B5" s="14">
+        <f ca="1">NOW()</f>
+        <v>46099.909397222225</v>
+      </c>
+      <c r="C5" s="17">
+        <f ca="1">B5</f>
+        <v>46099.909397222225</v>
+      </c>
+      <c r="D5" s="25">
+        <f ca="1">B5</f>
+        <v>46099.909397222225</v>
+      </c>
     </row>
     <row r="6" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="15"/>
+      <c r="B6" s="15">
+        <f ca="1">TODAY()</f>
+        <v>46099</v>
+      </c>
     </row>
     <row r="7" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2"/>
+      <c r="B8" s="2">
+        <f ca="1">DAY(B4)</f>
+        <v>18</v>
+      </c>
       <c r="D8" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="4"/>
+      <c r="E8" s="4">
+        <v>38965</v>
+      </c>
     </row>
     <row r="9" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="2"/>
+      <c r="B9" s="2">
+        <f ca="1">MONTH(B4)</f>
+        <v>3</v>
+      </c>
       <c r="D9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <f ca="1">_xlfn.DAYS(B4,E8)</f>
+        <v>7134</v>
+      </c>
     </row>
     <row r="10" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B10" s="2"/>
+      <c r="B10" s="2">
+        <f ca="1">YEAR(B4)</f>
+        <v>2026</v>
+      </c>
       <c r="D10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1">
+        <f ca="1" xml:space="preserve"> (YEAR(B4) - YEAR(E8)) * 12 + MONTH(B4) - MONTH(E8)</f>
+        <v>234</v>
+      </c>
     </row>
     <row r="11" spans="1:5" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1">
+        <f ca="1">E10/12</f>
+        <v>19.5</v>
+      </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
@@ -893,32 +1024,47 @@
       <c r="A1" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="24">
+        <f ca="1">NOW()</f>
+        <v>46099.909397222225</v>
+      </c>
     </row>
     <row r="2" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="3" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="7"/>
+      <c r="B3" s="7">
+        <f ca="1">HOUR(B1)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="B4" s="7"/>
+      <c r="B4" s="7">
+        <f ca="1">MINUTE(B1)</f>
+        <v>49</v>
+      </c>
     </row>
     <row r="5" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="7"/>
+      <c r="B5" s="7">
+        <f ca="1">SECOND(B1)</f>
+        <v>32</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="20"/>
+      <c r="B6" s="20">
+        <f ca="1">TIME(B3,B4,B5)</f>
+        <v>0.90939814814814823</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="8" spans="1:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
